--- a/output/pdf_financials_xlsx/SANU.xlsx
+++ b/output/pdf_financials_xlsx/SANU.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SANU.xlsx
+++ b/output/pdf_financials_xlsx/SANU.xlsx
@@ -2849,7 +2849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3432,29 +3432,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Current assets</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cash $</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
+          <t>June, 2024 June</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" s="5" t="n">
-        <v>0.832391</v>
+        <v>0.002023</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.150524</v>
+        <v>3e-05</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3465,29 +3457,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Notes 7 and 12) $</t>
+          <t>Net loss for the period $</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.56851</v>
+        <v>-2.885305</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.654811</v>
+        <v>-1.906684</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3498,31 +3490,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Loan payable (Note 8)</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CurrentDebt</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.449203</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.17639</v>
+        <v>0.189532</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3533,25 +3523,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Share capital (Note 9)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>11.953012</v>
+          <t>Accrued Interest</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>15.286028</v>
+        <v>0.00139</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3562,21 +3554,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Net changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reserves (Note 10)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
-        <v>0.923392</v>
+        <v>0.000267014</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1.058365</v>
+        <v>0.031652</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3587,25 +3587,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Net changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Non-controlling interests (Note 16)</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MinorityInterest</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.116183</v>
+        <v>0.007522</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.059277</v>
+        <v>-0.001766</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3619,18 +3623,26 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Net changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>June, 2024 June</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>0.002023</v>
+        <v>-1.557293</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.195278</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3646,24 +3658,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
+          <t>Net cash flows used in operating activities</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-2.885305</v>
+        <v>-3.71886</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-1.906684</v>
+        <v>-1.490598</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3679,24 +3691,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Cash received on acquisition</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>0.449203</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0.189532</v>
+        <v>0.754113</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3712,22 +3722,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accrued Interest</t>
+          <t>Property and equipment</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="5" t="n">
+        <v>-0.035127</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.00139</v>
+        <v>-0.050584</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3743,24 +3751,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Receivables</t>
+          <t>Exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.000267014</v>
+        <v>-2.40806</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.031652</v>
+        <v>-2.648701</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3776,24 +3784,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Net cash flows used in investing activities</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.007522</v>
+        <v>-1.689074</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.001766</v>
+        <v>-2.699285</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3809,24 +3817,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Proceeds from issuance of common shares</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-1.557293</v>
+        <v>3.00025</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.195278</v>
+        <v>3.45</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3842,24 +3850,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>-3.71886</v>
+        <v>-0.075268</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-1.490598</v>
+        <v>-0.116984</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3875,22 +3883,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cash received on acquisition</t>
+          <t>Proceeds from loan payable</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="n">
-        <v>0.754113</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.175</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3906,20 +3914,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Property and equipment</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Net cash flows provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
-        <v>-0.035127</v>
+        <v>2.924982</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.050584</v>
+        <v>3.508016</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3935,24 +3947,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Net decrease in cash</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-2.40806</v>
+        <v>-2.482952</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-2.648701</v>
+        <v>-0.681867</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3968,24 +3980,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>-1.689074</v>
+        <v>3.315343</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-2.699285</v>
+        <v>0.832391</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4006,19 +4018,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>3.00025</v>
+        <v>0.832391</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>3.45</v>
+        <v>0.150524</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4034,24 +4046,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Exploration and evaluation assets included in accounts payable</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-0.075268</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>-0.116984</v>
+        <v>0.133323</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4067,22 +4081,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Proceeds from loan payable</t>
+          <t>Residual value of warrants on private placement</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.175</v>
+      <c r="E40" s="5" t="n">
+        <v>0.277801</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4098,24 +4112,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net cash flows provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Fair value of finders’ warrants issued</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>2.924982</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>3.508016</v>
+        <v>0.031324</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -4131,24 +4143,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Net decrease in cash</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Shares issued for subscription receipts</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" s="5" t="n">
-        <v>-2.482952</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>-0.681867</v>
+        <v>3.265053</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4164,24 +4174,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Shares issued on conversion of special warrants</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>3.315343</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0.832391</v>
+        <v>3.331226</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4197,24 +4205,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Depreciation capitalized to exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.832391</v>
+        <v>0.019775</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.150524</v>
+        <v>0.034196</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -4230,26 +4238,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Balance at June 30,</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets included in accounts payable</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Balance at June 30,</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>0.133323</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.569006</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.116183</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4265,17 +4267,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>issued for private</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Residual value of warrants on private placement</t>
+          <t>issued for private placements (Note 9) 20,987,037 6,265,303 (3,265,053) - - - 3,000,250</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>0.277801</v>
+        <v>3.00025</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4296,17 +4298,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Share issuance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fair value of finders’ warrants issued</t>
+          <t>Share issuance costs (Note 9) - (384,393) - - 309,125 - (75,268)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>0.031324</v>
+        <v>-0.075268</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4327,17 +4329,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Special warrants</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shares issued for subscription receipts</t>
+          <t>Special warrants converted (Note 9) 10,446,000 3,331,226 - (3,331,226) - - -</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>3.265053</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4358,17 +4362,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>compensation (Note</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shares issued on conversion of special warrants</t>
+          <t>10 and 12) - - - - 449,203 - 449,203</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>3.331226</v>
+        <v>0.449203</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4389,24 +4393,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Acquisition of</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Depreciation capitalized to exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Acquisition of subsidiaries (Note 5) - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>0.019775</v>
+        <v>0.116183</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.034196</v>
+        <v>0.116183</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4422,20 +4422,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Balance at June 30,</t>
+          <t>Acquisition of</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Balance at June 30,</t>
+          <t>Net loss for the year - - - - - (2,885,305)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>8.569006</v>
+        <v>-2.885305</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.116183</v>
+        <v>-2.885305</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>issued for private placements (Note 9) 20,987,037 6,265,303 (3,265,053) - - - 3,000,250</t>
+          <t>issued for private placements (Note 9) 69,000,000 3,450,000 - - - - 3,450,000</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>3.00025</v>
+        <v>3.45</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 9) - (384,393) - - 309,125 - (75,268)</t>
+          <t>Share issuance costs (Note 9) - (116,984) - - - - (116,984)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>-0.075268</v>
+        <v>-0.116984</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4513,19 +4513,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Special warrants</t>
+          <t>compensation (Note</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Special warrants converted (Note 9) 10,446,000 3,331,226 - (3,331,226) - - -</t>
+          <t>10 and 12) - - - - 189,532 - 189,532</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="5" t="n">
+        <v>0.189532</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4546,17 +4544,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>compensation (Note</t>
+          <t>Reclass of expired</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10 and 12) - - - - 449,203 - 449,203</t>
+          <t>Reclass of expired options - - - - (54,559) 54,559 -</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>0.449203</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4577,20 +4577,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acquisition of</t>
+          <t>ownership of</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Acquisition of subsidiaries (Note 5) - - - - - - -</t>
+          <t>ownership of subsidiaries - - - - - 56,906 56,906</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>0.116183</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.116183</v>
+        <v>-0.056906</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4606,210 +4608,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Acquisition of</t>
+          <t>ownership of</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - - (2,885,305)</t>
+          <t>Net loss for the year - - - - - (1,906,684) (1,906,684)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>-2.885305</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>-2.885305</v>
+        <v>-1.906684</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>issued for private</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>issued for private placements (Note 9) 69,000,000 3,450,000 - - - - 3,450,000</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Share issuance</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Share issuance costs (Note 9) - (116,984) - - - - (116,984)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" s="5" t="n">
-        <v>-0.116984</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>compensation (Note</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>10 and 12) - - - - 189,532 - 189,532</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>0.189532</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Reclass of expired</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Reclass of expired options - - - - (54,559) 54,559 -</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>ownership of</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>ownership of subsidiaries - - - - - 56,906 56,906</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.056906</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>ownership of</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Net loss for the year - - - - - (1,906,684) (1,906,684)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>-1.906684</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/SANU.xlsx
+++ b/output/pdf_financials_xlsx/SANU.xlsx
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.923392</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.058365</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.859459</v>
       </c>
     </row>
     <row r="93">
@@ -3283,7 +3283,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.923392</v>
       </c>

--- a/output/pdf_financials_xlsx/SANU.xlsx
+++ b/output/pdf_financials_xlsx/SANU.xlsx
@@ -480,15 +480,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -502,15 +498,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
@@ -524,15 +516,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
@@ -546,15 +534,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>2.259347</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1.314003</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -568,15 +552,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
@@ -590,15 +570,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.464008</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.118604</v>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
@@ -612,15 +588,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>2.723355</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1.432607</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -634,15 +606,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-2.723355</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-1.432607</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -656,15 +624,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -678,15 +642,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
@@ -700,15 +660,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
@@ -722,15 +678,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
@@ -744,15 +696,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-2.885305</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-1.906684</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -766,15 +714,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -832,15 +776,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-2.885305</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-1.906684</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -854,15 +794,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
@@ -876,15 +812,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
@@ -982,15 +914,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-2.885305</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-1.906684</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1004,15 +932,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -1026,15 +950,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-2.885305</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-1.906684</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1070,15 +990,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -1656,13 +1572,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.145645</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.209908</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.141979</v>
       </c>
     </row>
     <row r="68">
@@ -2849,7 +2765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3436,21 +3352,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Current assets</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>June, 2024 June</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Cash $</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.832391</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.150524</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3461,29 +3385,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
+          <t>Accounts payable and accrued liabilities (Notes 7 and 12) $</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-2.885305</v>
+        <v>0.56851</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-1.906684</v>
+        <v>0.654811</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3494,29 +3418,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Loan payable (Note 8)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0.449203</v>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.189532</v>
+        <v>0.17639</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3527,27 +3453,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Non-cash items</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accrued Interest</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital (Note 9)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>11.953012</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.00139</v>
+        <v>15.286028</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3558,29 +3482,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Net changes in non-cash working capital items</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Receivables</t>
+          <t>Reserves (Note 10)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.000267014</v>
+        <v>0.923392</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.031652</v>
+        <v>1.058365</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3591,29 +3511,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Net changes in non-cash working capital items</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Non-controlling interests (Note 16)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>MinorityInterest</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.007522</v>
+        <v>0.116183</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-0.001766</v>
+        <v>0.059277</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3629,24 +3545,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Finder’s shares                                                                         384,588                              -</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>-1.557293</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0.195278</v>
+          <t>Finder’s shares                                                                         384,588                              - total</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3662,24 +3578,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Finder’s shares                                                                         384,588                              -</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Equity                                                                                3,536,230   3,450,000   (116,984)  189,532                             (4,480,604)   2,578,174     28,290,000    (1,374,493)  184,000  953,837                  (1,911,488) 28,720,030                                     Total $        $        $</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>-3.71886</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>-1.490598</v>
+        <v>0.059277</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3695,27 +3609,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>-  - -      - - -                                              an</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cash received on acquisition</t>
+          <t>-  - -      - - -                                              an form capital 11,953,012 3,450,000 (116,984) 15,286,028 28,290,000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>0.754113</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>42.489094</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.287559</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.374493</v>
       </c>
     </row>
     <row r="29">
@@ -3726,20 +3636,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>$        $        $                                     Share                                                                                                                                                                                                    notes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Property and equipment</t>
+          <t>$        $        $                                     Share                                                                                                                                                                                                    notes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" s="5" t="n">
-        <v>-0.035127</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>-0.050584</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3753,26 +3667,18 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>June, 2024 June</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>-2.40806</v>
+        <v>0.002023</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-2.648701</v>
+        <v>3e-05</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3788,24 +3694,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
+          <t>Net loss for the period $</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>-1.689074</v>
+        <v>-2.885305</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-2.699285</v>
+        <v>-1.906684</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3821,24 +3727,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3.00025</v>
+        <v>0.449203</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>3.45</v>
+        <v>0.189532</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3854,24 +3760,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>-0.075268</v>
+          <t>Accrued Interest</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.116984</v>
+        <v>0.00139</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3887,22 +3791,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Proceeds from loan payable</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.000267014</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.175</v>
+        <v>0.031652</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3918,24 +3824,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net cash flows provided by financing activities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2.924982</v>
+        <v>0.007522</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>3.508016</v>
+        <v>-0.001766</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3951,24 +3857,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Net decrease in cash</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-2.482952</v>
+        <v>-1.557293</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.681867</v>
+        <v>0.195278</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3984,24 +3890,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Net cash flows used in operating activities</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>3.315343</v>
+        <v>-3.71886</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.832391</v>
+        <v>-1.490598</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4017,24 +3923,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Cash received on acquisition</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>0.832391</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.150524</v>
+        <v>0.754113</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4050,26 +3954,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets included in accounts payable</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Property and equipment</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" s="5" t="n">
-        <v>0.133323</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.035127</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-0.050584</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4085,22 +3983,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Residual value of warrants on private placement</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>0.277801</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.40806</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>-2.648701</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4116,22 +4016,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fair value of finders’ warrants issued</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
-        <v>0.031324</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.689074</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>-2.699285</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -4147,22 +4049,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shares issued for subscription receipts</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Proceeds from issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
-        <v>3.265053</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.00025</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>3.45</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4178,22 +4082,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shares issued on conversion of special warrants</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
-        <v>3.331226</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.075268</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>-0.116984</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4209,24 +4115,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Depreciation capitalized to exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.019775</v>
+          <t>Proceeds from loan payable</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.034196</v>
+        <v>0.175</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -4242,20 +4146,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Balance at June 30,</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Balance at June 30,</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Net cash flows provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
-        <v>8.569006</v>
+        <v>2.924982</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.116183</v>
+        <v>3.508016</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4271,22 +4179,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>issued for private</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>issued for private placements (Note 9) 20,987,037 6,265,303 (3,265,053) - - - 3,000,250</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Net decrease in cash</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
-        <v>3.00025</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.482952</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>-0.681867</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4302,22 +4212,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Share issuance</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 9) - (384,393) - - 309,125 - (75,268)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
-        <v>-0.075268</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.315343</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.832391</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4333,24 +4245,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Special warrants</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Special warrants converted (Note 9) 10,446,000 3,331,226 - (3,331,226) - - -</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.832391</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.150524</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4366,17 +4278,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>compensation (Note</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10 and 12) - - - - 449,203 - 449,203</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Exploration and evaluation assets included in accounts payable</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
-        <v>0.449203</v>
+        <v>0.133323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4397,20 +4313,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Acquisition of</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Acquisition of subsidiaries (Note 5) - - - - - - -</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Residual value of warrants on private placement</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
-        <v>0.116183</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>0.116183</v>
+        <v>0.277801</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4426,20 +4348,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acquisition of</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - - (2,885,305)</t>
+          <t>Fair value of finders’ warrants issued</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>-2.885305</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>-2.885305</v>
+        <v>0.031324</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4455,17 +4379,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>issued for private</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>issued for private placements (Note 9) 69,000,000 3,450,000 - - - - 3,450,000</t>
+          <t>Shares issued for subscription receipts</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>3.45</v>
+        <v>3.265053</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4486,17 +4410,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Share issuance</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 9) - (116,984) - - - - (116,984)</t>
+          <t>Shares issued on conversion of special warrants</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>-0.116984</v>
+        <v>3.331226</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4517,22 +4441,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>compensation (Note</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10 and 12) - - - - 189,532 - 189,532</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Depreciation capitalized to exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
-        <v>0.189532</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019775</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.034196</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4548,24 +4474,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Reclass of expired</t>
+          <t>Balance at June 30,</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reclass of expired options - - - - (54,559) 54,559 -</t>
+          <t>Balance at June 30,</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E55" s="5" t="n">
+        <v>8.569006</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.116183</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4581,22 +4503,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ownership of</t>
+          <t>issued for private</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ownership of subsidiaries - - - - - 56,906 56,906</t>
+          <t>issued for private placements (Note 9) 20,987,037 6,265,303 (3,265,053) - - - 3,000,250</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>-0.056906</v>
+      <c r="E56" s="5" t="n">
+        <v>3.00025</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4612,24 +4534,958 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ownership of</t>
+          <t>Share issuance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - - (1,906,684) (1,906,684)</t>
+          <t>Share issuance costs (Note 9) - (384,393) - - 309,125 - (75,268)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
+        <v>-0.075268</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Special warrants</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Special warrants converted (Note 9) 10,446,000 3,331,226 - (3,331,226) - - -</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>compensation (Note</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>10 and 12) - - - - 449,203 - 449,203</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>0.449203</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Acquisition of</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Acquisition of subsidiaries (Note 5) - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>0.116183</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0.116183</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Acquisition of</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - - - (2,885,305)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>-2.885305</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>-2.885305</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>issued for private</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>issued for private placements (Note 9) 69,000,000 3,450,000 - - - - 3,450,000</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Share issuance</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Share issuance costs (Note 9) - (116,984) - - - - (116,984)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>-0.116984</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>compensation (Note</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>10 and 12) - - - - 189,532 - 189,532</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>0.189532</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Reclass of expired</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Reclass of expired options - - - - (54,559) 54,559 -</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ownership of</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ownership of subsidiaries - - - - - 56,906 56,906</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>-0.056906</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ownership of</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - - - (1,906,684) (1,906,684)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
         <v>-1.906684</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>0.93957</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.851562</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>1.3e-05</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Travel                                                                          13,452                    53,425</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Exploration expenses (Note</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>2.57392</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>6.238714</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>5e-06</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Travel                                                                          13,452                    53,425</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>0.189532</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.953837</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.001113</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Unrealized gain on investment (Note</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>6.729388</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>7e-06</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 12) $</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>1.301352</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0.93957</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0.094511</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.104308</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Office expenses</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0.5356070000000001</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.139508</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0.140068</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.085746</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0.464008</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.118604</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0.202765</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0.09575400000000001</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>0.079555</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0.053425</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note 10 and 12)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>0.449203</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.189532</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>-0.381764</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.178847</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-2.885305</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-1.906684</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Attributable to</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Equity holders of the parent</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>2.885305</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>1.906684</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Attributable to</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Attributable to</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Attributable to total</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>2.885305</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>1.906684</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Attributable to</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BASIC AND DILUTED LOSS PER SHARE FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING,</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BASIC AND DILUTED</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>61.721299</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>116.584186</v>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
